--- a/output/full_scan/batch_seq6_2026-10-01.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-01.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>956.00736129133</v>
+        <v>1126.007361291331</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>94.40000000000001</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.3695092906126</v>
+        <v>72.36950905925788</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>21.29514832380617</v>
+        <v>21.29514832950347</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>5.264745998104514</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.7233342392686499</v>
+        <v>0.723334239135121</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>914.5999808001992</v>
+        <v>1114.599980800199</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>50</v>
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.52924650055877</v>
+        <v>66.52924649150719</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>17.95678644119226</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.6105802325096097</v>
+        <v>0.6105802324873509</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6270</v>
+        <v>6175</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>907.2278885066468</v>
+        <v>1064.102266789363</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>30.55</v>
+        <v>76.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>59.98936272034152</v>
+        <v>60.49341051041078</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15.84438938323251</v>
+        <v>17.03522479698508</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.967716188614137</v>
+        <v>6.590315156381745</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2768735482285244</v>
+        <v>0.848219714143247</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6175</v>
+        <v>6270</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>894.1022667893634</v>
+        <v>1047.227888506647</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>76.3</v>
+        <v>30.55</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.49341051503491</v>
+        <v>59.98936270418365</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17.03522478288621</v>
+        <v>15.84438943881486</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6.590315156381745</v>
+        <v>1.967716188614137</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.8482197141877617</v>
+        <v>0.2768735481617616</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6292</v>
+        <v>6213</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>808.903485123278</v>
+        <v>1010.62586582572</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>67.2</v>
+        <v>642</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>59.82122029120498</v>
+        <v>72.25965391856826</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30.17658602220372</v>
+        <v>24.88268218979777</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.005378253880899</v>
+        <v>0.8477896988491738</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.0819907930709755</v>
+        <v>8.220708005761274</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6173</v>
+        <v>6209</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>807.8331140570375</v>
+        <v>942.7579625708994</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>302.5</v>
+        <v>82.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.90811773650238</v>
+        <v>59.29190148044587</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>38.69554064673044</v>
+        <v>26.99080242498385</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.599543650262021</v>
+        <v>0.9088724674802844</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-2.951938975985765</v>
+        <v>0.1515374599537078</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6227</v>
+        <v>6233</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>799.1246402009094</v>
+        <v>933.0506375453522</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>137</v>
+        <v>23.55</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.01040876670872</v>
+        <v>73.69444385354512</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>35.08991776196727</v>
+        <v>22.74041215458364</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.7326565879350632</v>
+        <v>3.624180861087128</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.7255991917589535</v>
+        <v>0.3473062684075139</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6202</v>
+        <v>6257</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>781.8702938960776</v>
+        <v>932.5603523378098</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60.1</v>
+        <v>256.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.11156432725057</v>
+        <v>67.89337317500552</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12.72469688624446</v>
+        <v>24.54056155417109</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.122068709402278</v>
+        <v>0.8148286474021569</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.5103916675948972</v>
+        <v>3.189673245915501</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6416</v>
+        <v>6205</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>771.6096497759836</v>
+        <v>929.2423335320497</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>120.5</v>
+        <v>71.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.07240643029658</v>
+        <v>60.54873488848858</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.31545962469692</v>
+        <v>25.71153203052175</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.170031196590154</v>
+        <v>0.9242333532049656</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1914985206852346</v>
+        <v>0.8846836102930127</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6209</v>
+        <v>6292</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>762.7579625708994</v>
+        <v>923.903485123278</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>82.7</v>
+        <v>67.2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.29190148547882</v>
+        <v>59.82122027053217</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.99080245397437</v>
+        <v>30.17658619766953</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9088724674802844</v>
+        <v>1.005378253880899</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1515374597200387</v>
+        <v>-0.08199079318224189</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6214</v>
+        <v>6227</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>752.2015223338955</v>
+        <v>914.12464020091</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>62.53975703403866</v>
+        <v>63.01040858671982</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.07004470213539</v>
+        <v>35.08991772770161</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4046676571395534</v>
+        <v>0.7326565879350632</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.455519817820488</v>
+        <v>0.7255991932054604</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6259</v>
+        <v>6202</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>737.4568928521644</v>
+        <v>911.8702938960778</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>31.8</v>
+        <v>60.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.91983909602488</v>
+        <v>59.11156430766096</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>11.8228291493931</v>
+        <v>12.72469695298579</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.846472844542112</v>
+        <v>3.122068709402278</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.3609167597998988</v>
+        <v>0.5103916675503863</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6233</v>
+        <v>6259</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>733.0506375453522</v>
+        <v>907.4568928521644</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23.55</v>
+        <v>31.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>73.69444392374056</v>
+        <v>62.91983909942322</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.74041214713692</v>
+        <v>11.82282918643333</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3.624180861087128</v>
+        <v>3.846472844542112</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3473062684075139</v>
+        <v>0.360916759822154</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6271</v>
+        <v>6438</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>731.9154676916125</v>
+        <v>901.653966903786</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>230.5</v>
+        <v>164.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.66396211255503</v>
+        <v>68.97504112676837</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.66676162680107</v>
+        <v>24.86429396167385</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6706715509115395</v>
+        <v>1.265396690378602</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.5718357133757452</v>
+        <v>1.712738301029343</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6472</v>
+        <v>6416</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>726.8370331088324</v>
+        <v>901.6096497759836</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>429.5</v>
+        <v>120.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53.60172390966706</v>
+        <v>66.07240628688356</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25.2662042171734</v>
+        <v>31.31545962293404</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.260498206227565</v>
+        <v>1.170031196590154</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.038112201858763</v>
+        <v>-0.1914985205517156</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6257</v>
+        <v>6414</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>712.5603523378098</v>
+        <v>889.4083140719059</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>256.5</v>
+        <v>402.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>67.8933731738461</v>
+        <v>57.79660562990635</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.54056150038724</v>
+        <v>21.65346712107576</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8148286474021569</v>
+        <v>1.375868281989976</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>3.189673245893248</v>
+        <v>4.637581903427222</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6435</v>
+        <v>6196</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>707.2935041013501</v>
+        <v>879.9994058435934</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>262</v>
+        <v>602</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.39557970087721</v>
+        <v>69.20011226464241</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10.15028633955699</v>
+        <v>21.55730537273352</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.259494103285634</v>
+        <v>1.099940584359345</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>2.873913621420628</v>
+        <v>7.370592543727021</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6263</v>
+        <v>6456</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>701.8315130848416</v>
+        <v>878.2219446578667</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>164</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.12196784388905</v>
+        <v>70.64291568072949</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15.14447317729456</v>
+        <v>28.28447768238558</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.215224583734582</v>
+        <v>1.922194465786674</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3302204114301497</v>
+        <v>2.658171295878349</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6284</v>
+        <v>6435</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>697.2121525787686</v>
+        <v>877.2935041013501</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>80.3</v>
+        <v>262</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>57.10846489571301</v>
+        <v>58.39557971850208</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9.581606283927719</v>
+        <v>10.15028629649878</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.6932798776885</v>
+        <v>2.259494103285634</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>1</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.4138753081610684</v>
+        <v>2.873913621242603</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6213</v>
+        <v>6432</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>695.6258658257204</v>
+        <v>875.2301042059507</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>642</v>
+        <v>69.8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>72.25965390549121</v>
+        <v>65.33376416950472</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.88268217208833</v>
+        <v>21.08175338627633</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8477896988491738</v>
+        <v>4.511358451064011</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>8.220708005471948</v>
+        <v>1.684857697980337</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6245</v>
+        <v>6278</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>684.864957203839</v>
+        <v>868.4624600285434</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>88.3</v>
+        <v>216.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.84049147075396</v>
+        <v>65.17492190660705</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.22566200719095</v>
+        <v>23.6429157811184</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4421984518870763</v>
+        <v>0.8058338888389115</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.520337614629248</v>
+        <v>2.302013908474124</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6205</v>
+        <v>6284</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>684.2423335320497</v>
+        <v>867.2121525787683</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>71.8</v>
+        <v>80.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.54873485304445</v>
+        <v>57.10846507649259</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>25.71153191252119</v>
+        <v>9.581606765701878</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9242333532049656</v>
+        <v>3.6932798776885</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.8846836105600595</v>
+        <v>0.41387530687033</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6275</v>
+        <v>6225</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>682.6065738823587</v>
+        <v>844.3734277590593</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>47.45</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.93724967280491</v>
+        <v>60.55062571517604</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31.83292317327754</v>
+        <v>25.86515159508586</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.001922282891943</v>
+        <v>0.5373427759059307</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.185706361675613</v>
+        <v>-0.9869483433700936</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6426</v>
+        <v>6263</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>677.171720017828</v>
+        <v>841.8315130848416</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>339.5</v>
+        <v>164</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.70550106983065</v>
+        <v>58.12196784388905</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>42.60784123498008</v>
+        <v>15.14447330050417</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5533886149797084</v>
+        <v>1.215224583734582</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-2.831165780510069</v>
+        <v>0.3302204113188993</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6432</v>
+        <v>6472</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>675.2301042059507</v>
+        <v>831.8370331088327</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>69.8</v>
+        <v>429.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>65.33376415797716</v>
+        <v>53.60172386441033</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.08175335472695</v>
+        <v>25.26620426629741</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4.511358451064011</v>
+        <v>1.260498206227565</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.684857698047095</v>
+        <v>1.038112203193999</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6290</v>
+        <v>6182</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>670.9500254184641</v>
+        <v>828.8690929809192</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>277.5</v>
+        <v>130</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.79829447763156</v>
+        <v>63.4689756605254</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.88631632964364</v>
+        <v>20.37084965975089</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5101278519772632</v>
+        <v>2.783871151365066</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0389305340986041</v>
+        <v>2.39366289114631</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6278</v>
+        <v>6275</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>663.4624600285434</v>
+        <v>822.6065738823586</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>216.5</v>
+        <v>47.45</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>65.17492190267029</v>
+        <v>61.93724961883604</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.64291579841538</v>
+        <v>31.83292317877502</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8058338888389115</v>
+        <v>1.001922282891943</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2.302013908474124</v>
+        <v>0.185706361742379</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6196</v>
+        <v>6274</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>659.9994058435934</v>
+        <v>816.8118083617364</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>602</v>
+        <v>1535</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>69.20011227026978</v>
+        <v>59.25687437830187</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.55730535657009</v>
+        <v>17.03404611000766</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.099940584359345</v>
+        <v>0.6027310833687199</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>7.370592544060791</v>
+        <v>18.44288665812945</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6182</v>
+        <v>6207</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>658.8690929809192</v>
+        <v>809.7971878689399</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>63.46897565544542</v>
+        <v>69.82169267005447</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.37084953252455</v>
+        <v>23.36637176705999</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.783871151365066</v>
+        <v>3.860114889682398</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2.393662891246448</v>
+        <v>4.061527519019763</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6274</v>
+        <v>6173</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>646.8118083617342</v>
+        <v>807.8331140570375</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1535</v>
+        <v>302.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.25687439049066</v>
+        <v>59.90811773949393</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.03404613999891</v>
+        <v>38.69554072199116</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6027310833687199</v>
+        <v>1.599543650262021</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>18.4428866551251</v>
+        <v>-2.951938976130464</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6414</v>
+        <v>6462</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>644.4083140719059</v>
+        <v>806.9525325139082</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>402.5</v>
+        <v>107</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.79660572776632</v>
+        <v>66.62330540805891</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21.65346708584904</v>
+        <v>17.78354177751477</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.375868281989976</v>
+        <v>3.295253251390813</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>4.637581902870899</v>
+        <v>1.04773189363493</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6462</v>
+        <v>6271</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>636.9525325139082</v>
+        <v>806.9154676916125</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>107</v>
+        <v>230.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>66.62330530923884</v>
+        <v>58.66396209590568</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.78354174444484</v>
+        <v>24.66676172262542</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.295253251390813</v>
+        <v>0.6706715509115395</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.047731894191293</v>
+        <v>-0.5718357133757452</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6438</v>
+        <v>6245</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>621.653966903786</v>
+        <v>799.8649572038396</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>164.5</v>
+        <v>88.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>68.97504111248324</v>
+        <v>59.84049137590033</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.86429396998264</v>
+        <v>25.22566205593714</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.265396690378602</v>
+        <v>0.4421984518870763</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.712738300918084</v>
+        <v>0.5203376148072878</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6207</v>
+        <v>6226</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>609.7971878689399</v>
+        <v>787.5120675943948</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>69.8216926870432</v>
+        <v>73.24484905810958</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23.36637175504433</v>
+        <v>48.91330391330266</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3.860114889682398</v>
+        <v>0.2202490377600425</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>4.061527519030891</v>
+        <v>0.4862120256882374</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6224</v>
+        <v>6197</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>607.3479318280969</v>
+        <v>785.6676602458318</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>81.7</v>
+        <v>330</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.47201540805341</v>
+        <v>62.58315183000566</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>37.13726554633276</v>
+        <v>15.18276051942597</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.630095549176057</v>
+        <v>1.012060657542472</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.490828969027611</v>
+        <v>2.644387374571444</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6291</v>
+        <v>6214</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>593.4779528383232</v>
+        <v>752.2015223338955</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>489</v>
+        <v>189</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.03642400523563</v>
+        <v>62.53975707547857</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.98825884064104</v>
+        <v>36.07004476269719</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3005088518333004</v>
+        <v>0.4046676571395534</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,11 +2425,11 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.927736886883288</v>
+        <v>-1.455519817820488</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>585.4181742146087</v>
+        <v>725.4181742146197</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>71.2</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.46788246556837</v>
+        <v>58.46788228795329</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13.71228488820772</v>
+        <v>13.71228488458353</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.7816005174247542</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3612500445783946</v>
+        <v>0.3612500455575811</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6166</v>
+        <v>6208</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>574.7165829659277</v>
+        <v>705.8352169782263</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>130</v>
+        <v>79.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.69778590027023</v>
+        <v>57.17412848132284</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>25.56516831115562</v>
+        <v>14.2456879897909</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5756767320287087</v>
+        <v>2.241599684175346</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>2.63536392943685</v>
+        <v>0.6494920675804767</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6456</v>
+        <v>6166</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>568.2219446578667</v>
+        <v>689.7165829659276</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>87.90000000000001</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>70.64291566921642</v>
+        <v>58.69778588968993</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.28447766266364</v>
+        <v>25.56516830123633</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.922194465786674</v>
+        <v>0.5756767320287087</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.658171295911724</v>
+        <v>2.635363929325582</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6208</v>
+        <v>6426</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>565.8352169782263</v>
+        <v>677.171720017828</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>79.5</v>
+        <v>339.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>57.17412846824615</v>
+        <v>56.70550107940743</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14.24568795002957</v>
+        <v>42.60784124913118</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.241599684175346</v>
+        <v>0.5533886149797084</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.6494920666012929</v>
+        <v>-2.831165780821642</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6197</v>
+        <v>6290</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>535.6676602458288</v>
+        <v>670.9500254184641</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>330</v>
+        <v>277.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>62.58315177004965</v>
+        <v>58.79829441182837</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15.18276050596186</v>
+        <v>28.88631640682136</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.012060657542472</v>
+        <v>0.5101278519772632</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>2.644387374460116</v>
+        <v>-0.0389305335422598</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6225</v>
+        <v>6204</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>534.3734277590593</v>
+        <v>633.7210335584382</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>104.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>60.55062573949958</v>
+        <v>60.28914714517831</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.8651517233447</v>
+        <v>26.68033162796681</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5373427759059307</v>
+        <v>1.166397062207925</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.9869483436260192</v>
+        <v>0.6091281236993247</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6417</v>
+        <v>6234</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>520.3564552037151</v>
+        <v>619.8993120152027</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>102</v>
+        <v>39.55</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>39.4529006543415</v>
+        <v>58.39571096317092</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>39.95858382723033</v>
+        <v>23.22443611835111</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.717017297550352</v>
+        <v>1.515421845561851</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2781913513307494</v>
+        <v>0.4755343086904691</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6204</v>
+        <v>6224</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>518.7210335584381</v>
+        <v>617.3479318280969</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>104.5</v>
+        <v>81.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>60.28914713662831</v>
+        <v>51.47201538813572</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>26.68033158991662</v>
+        <v>37.13726550877581</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.166397062207925</v>
+        <v>0.630095549176057</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.6091281237660855</v>
+        <v>-1.490828968949722</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6194</v>
+        <v>6164</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>505.1138025008845</v>
+        <v>615.6699295428791</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>30.1</v>
+        <v>12.55</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,49 +2884,49 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.9005665988532</v>
+        <v>60.65755759276061</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.71605737527987</v>
+        <v>22.32100533320535</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6417231042522483</v>
+        <v>0.4472071112722362</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0151785836595651</v>
+        <v>0.1225532737369284</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6234</v>
+        <v>6189</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>504.8993120152026</v>
+        <v>603.4219535814481</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>39.55</v>
+        <v>50.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>58.39571109071152</v>
+        <v>65.08776381886742</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.2244361183511</v>
+        <v>19.86016797327966</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.515421845561851</v>
+        <v>0.6288687383979825</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.4755343086237108</v>
+        <v>0.4030083878115461</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6418</v>
+        <v>6239</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>485.9492550749091</v>
+        <v>599.9384883479522</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>34.55</v>
+        <v>292.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.64110912906346</v>
+        <v>57.67201313426133</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>30.31128037138914</v>
+        <v>10.40527126574212</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.262552534110117</v>
+        <v>0.6207529491163822</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.138603980485643</v>
+        <v>1.29795057360918</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6239</v>
+        <v>6291</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>484.9384883479523</v>
+        <v>593.4779528383232</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>292.5</v>
+        <v>489</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.67201314614976</v>
+        <v>56.03642398754043</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10.40527123135397</v>
+        <v>27.98825885604898</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6207529491163822</v>
+        <v>0.3005088518333004</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,11 +3061,11 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.29795057360918</v>
+        <v>-1.927736885770649</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>477.9953151878229</v>
+        <v>592.9953151878229</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>24.9</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>58.08545185380862</v>
+        <v>58.08545179998274</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.04349105469118</v>
+        <v>19.04349105365329</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.1691300619087181</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0303555911707829</v>
+        <v>0.0303555912041675</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6281</v>
+        <v>6170</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>477.1130012445499</v>
+        <v>591.2250642357</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>51.1</v>
+        <v>49.15</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.80846883322235</v>
+        <v>62.55679981514469</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.23012348718571</v>
+        <v>17.92845022226118</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.200103256894549</v>
+        <v>1.148137265270002</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0020959984623989</v>
+        <v>0.0823373925621457</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6170</v>
+        <v>6449</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>476.2250642357002</v>
+        <v>576.9104063254175</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>49.15</v>
+        <v>230</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>62.55679956617695</v>
+        <v>54.87235260698147</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.92845024373129</v>
+        <v>11.98409593792028</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.148137265270002</v>
+        <v>2.210407713803517</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>1</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0823373924508732</v>
+        <v>1.448674640990636</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6223</v>
+        <v>6405</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>466.8297016980444</v>
+        <v>558.4714648906433</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>5030</v>
+        <v>45.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40.82611181534081</v>
+        <v>57.88367156777892</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.79623817721051</v>
+        <v>26.02999736062872</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.082970169804433</v>
+        <v>2.027968723475583</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-38.94620391244085</v>
+        <v>0.9830224804722832</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6443</v>
+        <v>6187</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>463.4370354044797</v>
+        <v>558.0102331101151</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>27.9</v>
+        <v>1275</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>57.83444582581415</v>
+        <v>52.46879387272171</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26.0014308079416</v>
+        <v>15.29071563452887</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6437035404479655</v>
+        <v>0.8127945090586501</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.5390685979219632</v>
+        <v>-1.826226117443813</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6419</v>
+        <v>6237</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>438.8249209273412</v>
+        <v>557.4117582576006</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>155</v>
+        <v>36.75</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.58948894093577</v>
+        <v>59.76943205232088</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11.5937595131969</v>
+        <v>21.97627893236012</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4295708441488945</v>
+        <v>1.935328184720017</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2480582311110348</v>
+        <v>0.3866441475704039</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6229</v>
+        <v>6419</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>438.7119056672807</v>
+        <v>553.8249209273413</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>24.15</v>
+        <v>155</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>59.30016827905613</v>
+        <v>53.58948894273149</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.4930705237144</v>
+        <v>11.59375952323382</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.511133207994418</v>
+        <v>0.4295708441488945</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.100033346620969</v>
+        <v>0.2480582309329998</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6165</v>
+        <v>6229</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>426.4817648879327</v>
+        <v>553.7119056672838</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>49.6</v>
+        <v>24.15</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.72301370884927</v>
+        <v>59.30016884147739</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.32650202874837</v>
+        <v>14.49307044379246</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6260243835203829</v>
+        <v>1.511133207994418</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1493347189113428</v>
+        <v>0.1000333463872997</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6191</v>
+        <v>6236</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>420.9877744318128</v>
+        <v>548.5113169284984</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>84.3</v>
+        <v>18.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>53.34465031119885</v>
+        <v>63.0726720470275</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>13.12709528908392</v>
+        <v>13.53651498820072</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9407867276444838</v>
+        <v>1.17827265229174</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.3742691449819384</v>
+        <v>1.576883132244258</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6187</v>
+        <v>6243</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>418.0102331101147</v>
+        <v>546.4736920409946</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>1275</v>
+        <v>40.55</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.46879385348899</v>
+        <v>53.11768150406197</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15.29071563110361</v>
+        <v>17.52878817886689</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8127945090586501</v>
+        <v>2.023847333304373</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.826226115441012</v>
+        <v>0.5321639045554718</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6206</v>
+        <v>6265</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>417.4459954904947</v>
+        <v>540.5860116435892</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>139</v>
+        <v>49.25</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.13932081602996</v>
+        <v>44.22993228230927</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.22862789399669</v>
+        <v>19.93562190482719</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3373978345595643</v>
+        <v>1.515292913821987</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1325173389913062</v>
+        <v>-0.0568671852923203</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6210</v>
+        <v>6191</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>408.7501109587664</v>
+        <v>530.9877744317951</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>17.9</v>
+        <v>84.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.12109336070388</v>
+        <v>53.34465042428105</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4.03536137088901</v>
+        <v>13.12709533948124</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.039717090732679</v>
+        <v>0.9407867276444838</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2186462482357941</v>
+        <v>0.3742691454270291</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6449</v>
+        <v>6210</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>406.9104063254175</v>
+        <v>523.7501109587664</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>230</v>
+        <v>17.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.87235254212939</v>
+        <v>52.12109334619055</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>11.98409590004076</v>
+        <v>4.035361374086869</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.210407713803517</v>
+        <v>1.039717090732679</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>1.448674641213191</v>
+        <v>0.2186462482357941</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6265</v>
+        <v>6417</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>400.5860116435893</v>
+        <v>520.3564552037153</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>49.25</v>
+        <v>102</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.22993226915634</v>
+        <v>39.45290054809085</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.93562185870621</v>
+        <v>39.95858390303736</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.515292913821987</v>
+        <v>0.717017297550352</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0568671852923203</v>
+        <v>0.278191351553291</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6244</v>
+        <v>6194</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>392.1186848183656</v>
+        <v>505.1138025008989</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>23.85</v>
+        <v>30.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>51.82580739803075</v>
+        <v>50.90056672747607</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.69730327935101</v>
+        <v>20.71605732638762</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.545713089857812</v>
+        <v>0.6417231042522483</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.2424066061179508</v>
+        <v>-0.0151785840045056</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6164</v>
+        <v>6418</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>390.6699295428791</v>
+        <v>485.9492550749091</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>12.55</v>
+        <v>34.55</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>60.65755761184242</v>
+        <v>51.64110919954339</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.32100530770175</v>
+        <v>30.31128039812518</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4472071112722362</v>
+        <v>1.262552534110117</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1225532737480572</v>
+        <v>-0.1386039803966245</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6405</v>
+        <v>6443</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>388.4714648906434</v>
+        <v>478.4370354044797</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>45.1</v>
+        <v>27.9</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>57.88367157834483</v>
+        <v>57.83444584286799</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>26.0299972492309</v>
+        <v>26.0014308079416</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.027968723475583</v>
+        <v>0.6437035404479655</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.98302248045003</v>
+        <v>0.5390685979108369</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6237</v>
+        <v>6281</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>387.4117582576006</v>
+        <v>477.1130012445416</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>36.75</v>
+        <v>51.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>59.76943196536288</v>
+        <v>46.80846883322235</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.97627889083797</v>
+        <v>11.23012366892449</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.935328184720017</v>
+        <v>1.200103256894549</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.386644147681678</v>
+        <v>0.0020959984401461</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6277</v>
+        <v>6223</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>365.0162888143816</v>
+        <v>466.8297016980444</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>77.7</v>
+        <v>5030</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.88373106589468</v>
+        <v>40.82611180484812</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.23170450919881</v>
+        <v>13.79623814955565</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.019218383914204</v>
+        <v>1.082970169804433</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0407799515419956</v>
+        <v>-38.94620390687747</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6189</v>
+        <v>6217</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>363.4219535814478</v>
+        <v>460.0272923137211</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>50.2</v>
+        <v>174.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>65.08776378630878</v>
+        <v>51.97574651793076</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.86016802035221</v>
+        <v>13.78318009414509</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6288687383979825</v>
+        <v>0.5885096966139497</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4030083880785969</v>
+        <v>0.4788565903369335</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6243</v>
+        <v>6183</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>356.4736920409946</v>
+        <v>458.6312417640204</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>40.55</v>
+        <v>92.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.11768152149757</v>
+        <v>54.22694861838622</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.52878811607698</v>
+        <v>11.72223384635427</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.023847333304373</v>
+        <v>0.546200261188292</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.532163904688999</v>
+        <v>0.0708588964639615</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6266</v>
+        <v>6228</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>350.9021171174962</v>
+        <v>444.9801791634337</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>24.95</v>
+        <v>18.15</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.30737797133118</v>
+        <v>55.52443834093224</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7.404029980663281</v>
+        <v>15.11574349337263</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7252024428639352</v>
+        <v>1.298017916343373</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0116459441254969</v>
+        <v>1.996770568224453</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6236</v>
+        <v>6165</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>348.5113169284984</v>
+        <v>426.4817648879327</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>18.7</v>
+        <v>49.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>63.0726720470275</v>
+        <v>54.72301389002157</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.53651510235069</v>
+        <v>16.32650204198399</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.17827265229174</v>
+        <v>0.6260243835203829</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.576883132244258</v>
+        <v>0.1493347187110515</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6415</v>
+        <v>6206</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>348.0936719574084</v>
+        <v>417.4459954904947</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>413</v>
+        <v>139</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.9240830583721</v>
+        <v>50.13932080501151</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8.254642624243102</v>
+        <v>17.22862789916118</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4154148918364889</v>
+        <v>0.3373978345595643</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.022552094495635</v>
+        <v>0.132517338768765</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6474</v>
+        <v>6235</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>345.7331905235792</v>
+        <v>409.2621202114969</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>35.45</v>
+        <v>39.15</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.76716039014264</v>
+        <v>53.87394364694242</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.64110342347671</v>
+        <v>15.58454513552855</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>3.224661262647181</v>
+        <v>0.7366715667511435</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>3</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0644447047796924</v>
+        <v>0.1259772979907608</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6217</v>
+        <v>6203</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>345.0272923137248</v>
+        <v>394.1187224738311</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>174.5</v>
+        <v>60.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.97574648673283</v>
+        <v>50.70253155279126</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.78318007130398</v>
+        <v>6.942640835298676</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5885096966139497</v>
+        <v>1.052645984901983</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.478856590325833</v>
+        <v>0.1599390033786685</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6183</v>
+        <v>6244</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>343.6312417640204</v>
+        <v>392.1186848183658</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>92.3</v>
+        <v>23.85</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>54.22694840507348</v>
+        <v>51.82580745179138</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11.72223383178014</v>
+        <v>18.69730327935101</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.546200261188292</v>
+        <v>1.545713089857812</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0708588964862211</v>
+        <v>0.2424066061068241</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6269</v>
+        <v>6277</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>337.5041809663976</v>
+        <v>365.0162888143816</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>65</v>
+        <v>77.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.93280623834472</v>
+        <v>47.8837310721604</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.9107738201522</v>
+        <v>14.23170464205928</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5009281315840165</v>
+        <v>1.019218383914204</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1810556880447509</v>
+        <v>-0.0407799516087661</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6451</v>
+        <v>6266</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>336.6164447747419</v>
+        <v>350.9021171174962</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>413</v>
+        <v>24.95</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.59229666635885</v>
+        <v>51.30737785511376</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7.421166917096309</v>
+        <v>7.404030132769091</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2423488890538111</v>
+        <v>0.7252024428639352</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.8060311127450532</v>
+        <v>0.011645944080986</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6285</v>
+        <v>6464</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>330.0942148853276</v>
+        <v>348.7466778753899</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>235.5</v>
+        <v>77</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.98379467459224</v>
+        <v>47.19795451840961</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.57425310224746</v>
+        <v>22.42595174076676</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.616956240534111</v>
+        <v>0.2529156190957056</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>1.36880360567363</v>
+        <v>-0.0543504015507422</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6464</v>
+        <v>6415</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>328.7466778753899</v>
+        <v>348.0936719574085</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.19795447821875</v>
+        <v>44.92408308438085</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>22.42595174076676</v>
+        <v>8.254642592807945</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.2529156190957056</v>
+        <v>0.4154148918364889</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0543504015062387</v>
+        <v>1.02255209271524</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6279</v>
+        <v>6474</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>323.0611657365571</v>
+        <v>345.7331905235792</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>113</v>
+        <v>35.45</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>41.81186171025201</v>
+        <v>39.76716057214631</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>34.55372461653502</v>
+        <v>13.64110345234041</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4915837038232319</v>
+        <v>3.224661262647181</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.3119941534263222</v>
+        <v>0.0644447044458768</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6177</v>
+        <v>6451</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>322.9880452716908</v>
+        <v>336.616444774742</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>46.65</v>
+        <v>413</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.32637781294156</v>
+        <v>45.5922967072005</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.50695020147578</v>
+        <v>7.421166897351338</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.07811779057014</v>
+        <v>0.2423488890538111</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1197456177784213</v>
+        <v>-0.806031112522489</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6192</v>
+        <v>6285</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>318.6276184058657</v>
+        <v>330.0942148853276</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>110</v>
+        <v>235.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,49 +4845,49 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.69687178108942</v>
+        <v>50.98379468081836</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>30.01794971103197</v>
+        <v>17.57425312285644</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.169184092881809</v>
+        <v>0.616956240534111</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.06934049191219489</v>
+        <v>1.36880360567363</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6412</v>
+        <v>6269</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>316.2701741429349</v>
+        <v>327.5041809663976</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.3663535250172</v>
+        <v>48.93280637615676</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23.13756463260224</v>
+        <v>12.91077400654582</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.078044301741676</v>
+        <v>0.5009281315840165</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2584458873484201</v>
+        <v>-0.1810556882672852</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6241</v>
+        <v>6279</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>306.594230423988</v>
+        <v>323.0611657365571</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>16.15</v>
+        <v>113</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>53.59542951158614</v>
+        <v>41.81186176772222</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12.80761227842866</v>
+        <v>34.55372472166617</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4452521527949192</v>
+        <v>0.4915837038232319</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.033984212735968</v>
+        <v>0.3119941539826878</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6184</v>
+        <v>6177</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>300.8100128754979</v>
+        <v>322.9880452716907</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>40.4</v>
+        <v>46.65</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46.93485024563254</v>
+        <v>45.32637771982728</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>32.52395743784365</v>
+        <v>16.50695015468779</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.1856281386537102</v>
+        <v>1.07811779057014</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1246976949494465</v>
+        <v>-0.1197456176449038</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6465</v>
+        <v>6192</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>300.2689716058921</v>
+        <v>318.627618405866</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>41.6</v>
+        <v>110</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>35.32945194280957</v>
+        <v>38.69687166988155</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.78949127105274</v>
+        <v>30.01794974919391</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4178966226257609</v>
+        <v>1.169184092881809</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1259086339302564</v>
+        <v>-0.069340491689642</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6235</v>
+        <v>6412</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>299.2621202114971</v>
+        <v>316.2701741429349</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>39.15</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>53.87394357430445</v>
+        <v>40.36635347549781</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.58454498542603</v>
+        <v>23.13756456972275</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7366715667511435</v>
+        <v>1.078044301741676</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1259772979685018</v>
+        <v>0.2584458872371358</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6442</v>
+        <v>6241</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>284.3380251306799</v>
+        <v>306.594230423988</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>1480</v>
+        <v>16.15</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.91349896926301</v>
+        <v>53.59542951158614</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.08137709336938</v>
+        <v>12.80761227842866</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.408937433407448</v>
+        <v>0.4452521527949192</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-19.76017304458632</v>
+        <v>0.033984212735968</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6198</v>
+        <v>6184</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>283.3951640360945</v>
+        <v>300.8100128754979</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0</v>
+        <v>40.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.74341866301612</v>
+        <v>46.93485032246772</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8.63059045392141</v>
+        <v>32.52395743784365</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0</v>
+        <v>0.1856281386537102</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.3271517677482995</v>
+        <v>0.1246976949271958</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6282</v>
+        <v>6465</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>282.9450416010325</v>
+        <v>300.2689716058921</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>43.3</v>
+        <v>41.6</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.79257997721701</v>
+        <v>35.3294520187558</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.46040272648416</v>
+        <v>11.78949101307626</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.8736323798530546</v>
+        <v>0.4178966226257609</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2482956435970781</v>
+        <v>0.1259086337204875</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6176</v>
+        <v>6161</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>280.0927258148125</v>
+        <v>285.8132633442478</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>49.96939227944608</v>
+        <v>52.0125255622584</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.61155647359664</v>
+        <v>11.07566086761984</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4959886453899398</v>
+        <v>0.3445128788606925</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.3051720907269099</v>
+        <v>0.2537307634721603</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6203</v>
+        <v>6442</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>279.118722473831</v>
+        <v>284.33802513068</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>60.3</v>
+        <v>1480</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>50.70253177280011</v>
+        <v>42.9134990317372</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6.942640919866164</v>
+        <v>12.08137706932407</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.052645984901983</v>
+        <v>0.408937433407448</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1599390034231745</v>
+        <v>-19.76017304636658</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6470</v>
+        <v>6198</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>274.5898734499031</v>
+        <v>283.3951640360946</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>42.7</v>
+        <v>0</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.65698220167683</v>
+        <v>44.74341866635909</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.17650504704666</v>
+        <v>8.630590470773171</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4636720209189391</v>
+        <v>0</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.04030235683526</v>
+        <v>-0.3271517677482995</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6215</v>
+        <v>6282</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>274.2006449432704</v>
+        <v>282.9450416010323</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>47.09974036203747</v>
+        <v>45.79258005532147</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9.57687077625091</v>
+        <v>15.46040269312438</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5106107530989402</v>
+        <v>0.8736323798530546</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0362446748996021</v>
+        <v>0.2482956434858099</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6411</v>
+        <v>6176</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>273.7134622599322</v>
+        <v>280.0927258148125</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.82825960478591</v>
+        <v>49.96939199723186</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>7.372969624195102</v>
+        <v>15.61155658407628</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8139101709126358</v>
+        <v>0.4959886453899398</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1003837515453824</v>
+        <v>-0.3051720901548099</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6261</v>
+        <v>6283</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>266.6311711644726</v>
+        <v>274.8910859256393</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>19.3</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>51.91214885389365</v>
+        <v>49.72251662239884</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.16331140653698</v>
+        <v>20.31954352640942</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7349375112750099</v>
+        <v>0.4356035478952397</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.3734421142292449</v>
+        <v>0.1251729061466363</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6446</v>
+        <v>6470</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>264.8709285419962</v>
+        <v>274.5898734499031</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1170</v>
+        <v>42.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.9759245655888</v>
+        <v>47.65698260293883</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.65562574011998</v>
+        <v>21.17650503428106</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6962900534987729</v>
+        <v>0.4636720209189391</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-4.911029171216676</v>
+        <v>0.040302355967344</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6185</v>
+        <v>6215</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>262.1379618019273</v>
+        <v>274.2006449432705</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>12.6</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45.90333939111532</v>
+        <v>47.09974004688119</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>23.15068810397668</v>
+        <v>9.576870779050424</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.8177762603097137</v>
+        <v>0.5106107530989402</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0390286770853488</v>
+        <v>0.036244677570106</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6201</v>
+        <v>6411</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>254.9224999658662</v>
+        <v>273.7134622599322</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>44.55</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45.83040124147389</v>
+        <v>48.82825957675713</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>27.84021902463761</v>
+        <v>7.372969695116008</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8297683039851714</v>
+        <v>0.8139101709126358</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0284679979198936</v>
+        <v>0.1003837516566532</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6167</v>
+        <v>6261</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>245.5584502926201</v>
+        <v>266.6311711644726</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>10.25</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.95036818994643</v>
+        <v>51.91214880510345</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.43034616345898</v>
+        <v>12.16331144875343</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9435725048757748</v>
+        <v>0.7349375112750099</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.02882665795249</v>
+        <v>0.3734421144740331</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6228</v>
+        <v>6446</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>244.9801791634337</v>
+        <v>264.8709285419962</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>18.15</v>
+        <v>1170</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>55.52443832730572</v>
+        <v>40.97592455109632</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.11574352841662</v>
+        <v>18.65562574556345</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.298017916343373</v>
+        <v>0.6962900534987729</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>1.996770568446998</v>
+        <v>-4.911029171216676</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6163</v>
+        <v>6185</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>244.5085049235388</v>
+        <v>262.1379618019273</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>41.4</v>
+        <v>12.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>49.75726333131209</v>
+        <v>45.90333945874168</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.80271977021488</v>
+        <v>23.15068812280106</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.013399440847198</v>
+        <v>0.8177762603097137</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.169895020121563</v>
+        <v>0.0390286770408395</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6246</v>
+        <v>6201</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>217.231997768386</v>
+        <v>254.9224999658662</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>12.7</v>
+        <v>44.55</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,25 +5958,25 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>47.60167647139504</v>
+        <v>45.83040120183964</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>26.08659666492145</v>
+        <v>27.84021904318305</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.329102579476531</v>
+        <v>0.8297683039851714</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0112886324414786</v>
+        <v>0.0284679979198936</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6230</v>
+        <v>6167</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>205.6206411587519</v>
+        <v>245.5584502926201</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>111</v>
+        <v>10.25</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.02801530308616</v>
+        <v>45.95036865290073</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.91808549946325</v>
+        <v>12.43034615056805</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.554202859600871</v>
+        <v>0.9435725048757748</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.2709893398396522</v>
+        <v>0.0288266578380692</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6409</v>
+        <v>6163</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>204.5914513081528</v>
+        <v>244.5085049235374</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>891</v>
+        <v>41.4</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.43935327509045</v>
+        <v>49.75726336801233</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.1211903389458</v>
+        <v>10.8027197845829</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4906897284114171</v>
+        <v>1.013399440847198</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>2.460572257402646</v>
+        <v>0.1698950202105786</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6216</v>
+        <v>6230</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>191.4488618853321</v>
+        <v>225.6206411587519</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>19.75</v>
+        <v>111</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.61521954744963</v>
+        <v>50.02801536868266</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>39.34254746849702</v>
+        <v>14.91808552760623</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4777504315016493</v>
+        <v>0.554202859600871</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.09855139605026091</v>
+        <v>0.2709893396171246</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6272</v>
+        <v>6246</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>188.6606771228871</v>
+        <v>217.231997768386</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25.2</v>
+        <v>12.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.72343503122143</v>
+        <v>47.60167640516409</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>25.0368118752379</v>
+        <v>26.08659653410995</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3173105929184466</v>
+        <v>0.329102579476531</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.3035151347153247</v>
+        <v>0.0112886324637351</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6188</v>
+        <v>6409</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>172.1503982785015</v>
+        <v>204.5914513081526</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>62.1</v>
+        <v>891</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,49 +6223,49 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>35.71342047022232</v>
+        <v>42.43935338840352</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>29.82420127436689</v>
+        <v>17.12119041472884</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5403962944694495</v>
+        <v>0.4906897284114171</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1820814277916413</v>
+        <v>2.460572236261097</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6220</v>
+        <v>6216</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>168.9357121648306</v>
+        <v>191.4488618853321</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>25.3</v>
+        <v>19.75</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,49 +6276,49 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.04137926752534</v>
+        <v>40.61521947149753</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10.37374083049119</v>
+        <v>39.34254757122261</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7579873583652941</v>
+        <v>0.4777504315016493</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.07685208517720719</v>
+        <v>0.09855139605026091</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6283</v>
+        <v>6272</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>159.8910859256394</v>
+        <v>188.6606771228871</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,25 +6329,25 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.72251607927664</v>
+        <v>42.72343505869527</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.31954349218566</v>
+        <v>25.03681201398846</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4356035478952397</v>
+        <v>0.3173105929184466</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1251729061800176</v>
+        <v>-0.3035151346374368</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6161</v>
+        <v>6188</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>145.8132633442478</v>
+        <v>172.1503982785012</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>50.3</v>
+        <v>62.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>52.01252556559952</v>
+        <v>35.7134205183831</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.07566080922126</v>
+        <v>29.82420132498319</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3445128788606925</v>
+        <v>0.5403962944694495</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.2537307635166637</v>
+        <v>0.1820814280586857</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6276</v>
+        <v>6220</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>138.5986596322112</v>
+        <v>168.9357121648307</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>19.65</v>
+        <v>25.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.61191178348922</v>
+        <v>42.04137957026309</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.01777507588041</v>
+        <v>10.37374137771673</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4507417947597085</v>
+        <v>0.7579873583652941</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,62 +6453,115 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.009828619174083401</v>
+        <v>0.0768520848322676</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
+        <v>6276</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>安鈦克</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>138.598659632214</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>47.61191225650089</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>16.01777485927285</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.4507417947597085</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.009828619841708099</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
         <v>6222</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>立軒</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
         <v>100.7579474397958</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>18.70251387340151</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>8.330722279769503</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>-1.253016364329143</v>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>18.70251387243654</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>8.330722318515738</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-1.253016364373649</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
